--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T06:02:54+00:00</t>
+    <t>2025-04-17T08:21:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T08:21:49+00:00</t>
+    <t>2025-04-17T08:44:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,74 +307,76 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -390,28 +395,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T08:44:33+00:00</t>
+    <t>2025-04-17T09:22:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,22 +60,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T09:22:19+00:00</t>
+    <t>2025-04-28T07:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Belgium</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -27,6 +27,12 @@
     <t>https://www.ehealth.fgov.be/standards/fhir/pss/ValueSet/PSSRatingTypesVS</t>
   </si>
   <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>OID:2.16.840.1.113883.2.51.22.2.48.9</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
@@ -54,13 +60,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
+    <t>false</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:30:14+00:00</t>
+    <t>2025-05-13T10:14:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +81,7 @@
     <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
   </si>
   <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -248,7 +254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -337,15 +343,15 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>22</v>
@@ -363,20 +369,28 @@
       <c r="A14" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s" s="2">
         <v>28</v>
+      </c>
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -395,28 +409,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:14:30+00:00</t>
+    <t>2025-05-13T11:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:53:59+00:00</t>
+    <t>2025-05-13T11:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:54:01+00:00</t>
+    <t>2025-05-14T06:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:55:38+00:00</t>
+    <t>2025-05-14T06:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:56:25+00:00</t>
+    <t>2025-05-14T07:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:30:16+00:00</t>
+    <t>2025-05-14T07:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:52:33+00:00</t>
+    <t>2025-05-14T07:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:53:22+00:00</t>
+    <t>2025-05-14T15:00:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T15:00:45+00:00</t>
+    <t>2025-05-22T14:06:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -27,12 +27,6 @@
     <t>https://www.ehealth.fgov.be/standards/fhir/pss/ValueSet/PSSRatingTypesVS</t>
   </si>
   <si>
-    <t>Identifier</t>
-  </si>
-  <si>
-    <t>OID:2.16.840.1.113883.2.51.22.2.48.9</t>
-  </si>
-  <si>
     <t>Version</t>
   </si>
   <si>
@@ -66,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:06:49+00:00</t>
+    <t>2025-05-22T14:43:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -254,7 +248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -343,15 +337,15 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>22</v>
@@ -369,28 +363,20 @@
       <c r="A14" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B14" t="s" s="2">
-        <v>26</v>
-      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -409,28 +395,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:43:01+00:00</t>
+    <t>2025-05-22T14:52:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:52:21+00:00</t>
+    <t>2025-06-11T04:00:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T04:00:37+00:00</t>
+    <t>2025-06-26T13:57:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-26T13:57:34+00:00</t>
+    <t>2025-07-16T16:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T16:47:23+00:00</t>
+    <t>2025-07-16T16:49:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-PSSRatingTypesVS.xlsx
+++ b/branches/master/ValueSet-PSSRatingTypesVS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -27,6 +27,12 @@
     <t>https://www.ehealth.fgov.be/standards/fhir/pss/ValueSet/PSSRatingTypesVS</t>
   </si>
   <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>OID:2.16.840.1.113883.2.51.22.2.48.9</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
@@ -60,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T16:49:48+00:00</t>
+    <t>2025-07-18T09:14:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -248,7 +254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -337,15 +343,15 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>22</v>
@@ -363,20 +369,28 @@
       <c r="A14" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s" s="2">
         <v>28</v>
+      </c>
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -395,28 +409,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
